--- a/assets/templates/Plantilla_Importacion_Botanika_v7.1.xlsx
+++ b/assets/templates/Plantilla_Importacion_Botanika_v7.1.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R5fe45952e4d54f38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="2" r:id="Red52769682d04464"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combos" sheetId="3" r:id="R0e5d5ea5fb954112"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductosCombo" sheetId="4" r:id="Rcad29d7960cf4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Rd56a64f9ad364726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="2" r:id="Rccad1893612f49aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combos" sheetId="3" r:id="R9298d489022c4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductosCombo" sheetId="4" r:id="R67ba9544a9ff4bd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -68,7 +68,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -119,6 +119,7 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -449,6 +450,14 @@
       <x:c r="E15" s="15"/>
       <x:c r="F15" s="15"/>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>Consejo Botanika</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="str">
+        <x:v>En Productos use consejo_botanika para una recomendación breve de uso. Si queda vacío, el sitio mostrará un consejo general.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -468,7 +477,7 @@
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="44" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
@@ -501,27 +510,30 @@
         <x:v>descripcion</x:v>
       </x:c>
       <x:c r="H1" s="21" t="str">
+        <x:v>consejo_botanika</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str">
         <x:v>imagen</x:v>
       </x:c>
-      <x:c r="I1" s="21" t="str">
+      <x:c r="J1" s="21" t="str">
         <x:v>disponible</x:v>
       </x:c>
-      <x:c r="J1" s="21" t="str">
+      <x:c r="K1" s="21" t="str">
         <x:v>nuevo</x:v>
       </x:c>
-      <x:c r="K1" s="21" t="str">
+      <x:c r="L1" s="21" t="str">
         <x:v>destacado</x:v>
       </x:c>
-      <x:c r="L1" s="21" t="str">
+      <x:c r="M1" s="21" t="str">
         <x:v>oferta</x:v>
       </x:c>
-      <x:c r="M1" s="21" t="str">
+      <x:c r="N1" s="21" t="str">
         <x:v>prioridad</x:v>
       </x:c>
-      <x:c r="N1" s="21" t="str">
+      <x:c r="O1" s="21" t="str">
         <x:v>colores</x:v>
       </x:c>
-      <x:c r="O1" s="21" t="str">
+      <x:c r="P1" t="str">
         <x:v>galeria</x:v>
       </x:c>
     </x:row>
@@ -547,28 +559,31 @@
       <x:c r="G2" t="str">
         <x:v>Descripción breve del producto.</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H2" s="15" t="str">
+        <x:v>Para un acabado uniforme, aplique el producto en capas ligeras y difumine bien.</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
         <x:v>assets/img/products/base-ejemplo.jpg</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>Sí</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>Sí</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>No</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="L2" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="M2" t="n">
+      <x:c r="M2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N2" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="N2" t="str">
+      <x:c r="O2" t="str">
         <x:v>Nude|#CDA88C|assets/img/products/base-ejemplo-nude.jpg; Beige|#B98C70|assets/img/products/base-ejemplo-beige.jpg</x:v>
       </x:c>
-      <x:c r="O2" t="str">
+      <x:c r="P2" t="str">
         <x:v>assets/img/products/base-ejemplo-2.jpg; assets/img/products/base-ejemplo-3.jpg</x:v>
       </x:c>
     </x:row>
